--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T05:44:07+00:00</t>
+    <t>2026-04-14T09:50:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T09:50:31+00:00</t>
+    <t>2026-04-15T07:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:34+00:00</t>
+    <t>2026-04-16T14:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T14:06:50+00:00</t>
+    <t>2026-04-16T14:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T14:18:04+00:00</t>
+    <t>2026-04-20T12:22:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T12:22:27+00:00</t>
+    <t>2026-04-27T11:51:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T11:51:59+00:00</t>
+    <t>2026-05-06T21:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T21:53:27+00:00</t>
+    <t>2026-05-07T11:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:13:00+00:00</t>
+    <t>2026-05-08T13:26:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T13:26:23+00:00</t>
+    <t>2026-05-08T22:41:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T22:41:29+00:00</t>
+    <t>2026-05-12T10:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T10:06:01+00:00</t>
+    <t>2026-05-12T14:33:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T14:33:10+00:00</t>
+    <t>2026-05-15T11:23:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/1.0.0-draft/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:23:32+00:00</t>
+    <t>2026-05-19T15:25:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
